--- a/AAII_Financials/Yearly/XRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XRX_YR_FIN.xlsx
@@ -783,10 +783,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5019000</v>
+        <v>4995000</v>
       </c>
       <c r="E9" s="3">
-        <v>4261000</v>
+        <v>4210000</v>
       </c>
       <c r="F9" s="3">
         <v>4572000</v>
@@ -834,10 +834,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2003000</v>
+        <v>2027000</v>
       </c>
       <c r="E10" s="3">
-        <v>1960000</v>
+        <v>2011000</v>
       </c>
       <c r="F10" s="3">
         <v>2314000</v>
@@ -1008,10 +1008,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>195000</v>
+        <v>219000</v>
       </c>
       <c r="E14" s="3">
-        <v>1166000</v>
+        <v>1217000</v>
       </c>
       <c r="F14" s="3">
         <v>138000</v>
@@ -1128,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7031000</v>
+        <v>7007000</v>
       </c>
       <c r="E17" s="3">
-        <v>6142000</v>
+        <v>6091000</v>
       </c>
       <c r="F17" s="3">
         <v>6559000</v>
@@ -1179,10 +1179,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-9000</v>
+        <v>15000</v>
       </c>
       <c r="E18" s="3">
-        <v>79000</v>
+        <v>130000</v>
       </c>
       <c r="F18" s="3">
         <v>327000</v>
@@ -1302,10 +1302,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>24000</v>
+        <v>48000</v>
       </c>
       <c r="E21" s="3">
-        <v>128000</v>
+        <v>179000</v>
       </c>
       <c r="F21" s="3">
         <v>205000</v>
